--- a/artfynd/A 57378-2020 artfynd.xlsx
+++ b/artfynd/A 57378-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122777292</v>
       </c>
       <c r="B2" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>122815707</v>
       </c>
       <c r="B3" t="n">
-        <v>90905</v>
+        <v>90909</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 57378-2020 artfynd.xlsx
+++ b/artfynd/A 57378-2020 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>122815707</v>
       </c>
       <c r="B3" t="n">
-        <v>90909</v>
+        <v>90917</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 57378-2020 artfynd.xlsx
+++ b/artfynd/A 57378-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122777292</v>
       </c>
       <c r="B2" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>122815707</v>
       </c>
       <c r="B3" t="n">
-        <v>90917</v>
+        <v>90920</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 57378-2020 artfynd.xlsx
+++ b/artfynd/A 57378-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122777292</v>
       </c>
       <c r="B2" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>122815707</v>
       </c>
       <c r="B3" t="n">
-        <v>90920</v>
+        <v>90922</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 57378-2020 artfynd.xlsx
+++ b/artfynd/A 57378-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122777292</v>
       </c>
       <c r="B2" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>122815707</v>
       </c>
       <c r="B3" t="n">
-        <v>90922</v>
+        <v>90928</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 57378-2020 artfynd.xlsx
+++ b/artfynd/A 57378-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -885,6 +885,341 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>128296497</v>
+      </c>
+      <c r="B4" t="n">
+        <v>92644</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>788</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gul taggsvamp</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hydnellum geogenium</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Fr.) Banker</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Båshöjden, Båshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>477397</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6593421</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128296452</v>
+      </c>
+      <c r="B5" t="n">
+        <v>92644</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>788</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Gul taggsvamp</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hydnellum geogenium</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.) Banker</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Båshöjden, Båshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>477400</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6593418</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128296673</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57832</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Båshöjden, Båshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>477345</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6593397</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 57378-2020 artfynd.xlsx
+++ b/artfynd/A 57378-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1220,6 +1220,667 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128373243</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57669</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Båshöjden, Båshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>477342</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6593444</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>I torkande gran.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128373432</v>
+      </c>
+      <c r="B8" t="n">
+        <v>91984</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1339</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Brandticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Pycnoporellus fulgens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Båshöjden, Båshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>477404</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6593461</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128374330</v>
+      </c>
+      <c r="B9" t="n">
+        <v>91320</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Båshöjden, Båshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>477309</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6593359</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128373961</v>
+      </c>
+      <c r="B10" t="n">
+        <v>91369</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Båshöjden, Båshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>477355</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6593441</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128373501</v>
+      </c>
+      <c r="B11" t="n">
+        <v>91320</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Båshöjden, Båshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>477404</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6593461</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128374049</v>
+      </c>
+      <c r="B12" t="n">
+        <v>91320</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Båshöjden, Båshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>477371</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6593451</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 57378-2020 artfynd.xlsx
+++ b/artfynd/A 57378-2020 artfynd.xlsx
@@ -1348,10 +1348,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128373432</v>
+        <v>128374330</v>
       </c>
       <c r="B8" t="n">
-        <v>91984</v>
+        <v>91320</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1359,21 +1359,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1339</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1383,10 +1383,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>477404</v>
+        <v>477309</v>
       </c>
       <c r="R8" t="n">
-        <v>6593461</v>
+        <v>6593359</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1455,32 +1455,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128374330</v>
+        <v>128373961</v>
       </c>
       <c r="B9" t="n">
-        <v>91320</v>
+        <v>91369</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>1204</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1490,10 +1490,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>477309</v>
+        <v>477355</v>
       </c>
       <c r="R9" t="n">
-        <v>6593359</v>
+        <v>6593441</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1525,7 +1525,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1562,32 +1562,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128373961</v>
+        <v>128373432</v>
       </c>
       <c r="B10" t="n">
-        <v>91369</v>
+        <v>91984</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1204</v>
+        <v>1339</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1597,10 +1597,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>477355</v>
+        <v>477404</v>
       </c>
       <c r="R10" t="n">
-        <v>6593441</v>
+        <v>6593461</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1632,7 +1632,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 57378-2020 artfynd.xlsx
+++ b/artfynd/A 57378-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -890,7 +890,7 @@
         <v>128296497</v>
       </c>
       <c r="B4" t="n">
-        <v>92644</v>
+        <v>92652</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>128296452</v>
       </c>
       <c r="B5" t="n">
-        <v>92644</v>
+        <v>92652</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
         <v>128296673</v>
       </c>
       <c r="B6" t="n">
-        <v>57832</v>
+        <v>57833</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1225,7 +1225,7 @@
         <v>128373243</v>
       </c>
       <c r="B7" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
         <v>128374330</v>
       </c>
       <c r="B8" t="n">
-        <v>91320</v>
+        <v>91325</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1455,32 +1455,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128373961</v>
+        <v>128373432</v>
       </c>
       <c r="B9" t="n">
-        <v>91369</v>
+        <v>91989</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1204</v>
+        <v>1339</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1490,10 +1490,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>477355</v>
+        <v>477404</v>
       </c>
       <c r="R9" t="n">
-        <v>6593441</v>
+        <v>6593461</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1525,7 +1525,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1562,32 +1562,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128373432</v>
+        <v>128373961</v>
       </c>
       <c r="B10" t="n">
-        <v>91984</v>
+        <v>91374</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1339</v>
+        <v>1204</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1597,10 +1597,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>477404</v>
+        <v>477355</v>
       </c>
       <c r="R10" t="n">
-        <v>6593461</v>
+        <v>6593441</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1632,7 +1632,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1672,7 +1672,7 @@
         <v>128373501</v>
       </c>
       <c r="B11" t="n">
-        <v>91320</v>
+        <v>91325</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
         <v>128374049</v>
       </c>
       <c r="B12" t="n">
-        <v>91320</v>
+        <v>91325</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1880,6 +1880,569 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128482512</v>
+      </c>
+      <c r="B13" t="n">
+        <v>91325</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Båshöjden, Båshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>477334</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6593397</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128482605</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57833</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Båshöjden, Båshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>477359</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6593404</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128483143</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57833</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Båshöjden, Båshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>477372</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6593484</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128483246</v>
+      </c>
+      <c r="B16" t="n">
+        <v>91325</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Båshöjden, Båshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>477422</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6593431</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>128483569</v>
+      </c>
+      <c r="B17" t="n">
+        <v>91374</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Båshöjden, Båshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>477376</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6593486</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 57378-2020 artfynd.xlsx
+++ b/artfynd/A 57378-2020 artfynd.xlsx
@@ -890,7 +890,7 @@
         <v>128296497</v>
       </c>
       <c r="B4" t="n">
-        <v>92652</v>
+        <v>92744</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>128296452</v>
       </c>
       <c r="B5" t="n">
-        <v>92652</v>
+        <v>92744</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
         <v>128296673</v>
       </c>
       <c r="B6" t="n">
-        <v>57833</v>
+        <v>57845</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1225,7 +1225,7 @@
         <v>128373243</v>
       </c>
       <c r="B7" t="n">
-        <v>57670</v>
+        <v>57682</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
         <v>128374330</v>
       </c>
       <c r="B8" t="n">
-        <v>91325</v>
+        <v>91417</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>128373432</v>
       </c>
       <c r="B9" t="n">
-        <v>91989</v>
+        <v>92081</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         <v>128373961</v>
       </c>
       <c r="B10" t="n">
-        <v>91374</v>
+        <v>91466</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1672,7 +1672,7 @@
         <v>128373501</v>
       </c>
       <c r="B11" t="n">
-        <v>91325</v>
+        <v>91417</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
         <v>128374049</v>
       </c>
       <c r="B12" t="n">
-        <v>91325</v>
+        <v>91417</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1886,7 +1886,7 @@
         <v>128482512</v>
       </c>
       <c r="B13" t="n">
-        <v>91325</v>
+        <v>91417</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
         <v>128482605</v>
       </c>
       <c r="B14" t="n">
-        <v>57833</v>
+        <v>57845</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2114,7 +2114,7 @@
         <v>128483143</v>
       </c>
       <c r="B15" t="n">
-        <v>57833</v>
+        <v>57845</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>128483246</v>
       </c>
       <c r="B16" t="n">
-        <v>91325</v>
+        <v>91417</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2342,7 +2342,7 @@
         <v>128483569</v>
       </c>
       <c r="B17" t="n">
-        <v>91374</v>
+        <v>91466</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 57378-2020 artfynd.xlsx
+++ b/artfynd/A 57378-2020 artfynd.xlsx
@@ -1348,10 +1348,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128374330</v>
+        <v>128373432</v>
       </c>
       <c r="B8" t="n">
-        <v>91417</v>
+        <v>92081</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1359,21 +1359,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>1339</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1383,10 +1383,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>477309</v>
+        <v>477404</v>
       </c>
       <c r="R8" t="n">
-        <v>6593359</v>
+        <v>6593461</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1455,32 +1455,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128373432</v>
+        <v>128373961</v>
       </c>
       <c r="B9" t="n">
-        <v>92081</v>
+        <v>91466</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1339</v>
+        <v>1204</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1490,10 +1490,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>477404</v>
+        <v>477355</v>
       </c>
       <c r="R9" t="n">
-        <v>6593461</v>
+        <v>6593441</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1525,7 +1525,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1562,32 +1562,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128373961</v>
+        <v>128374330</v>
       </c>
       <c r="B10" t="n">
-        <v>91466</v>
+        <v>91417</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1204</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1597,10 +1597,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>477355</v>
+        <v>477309</v>
       </c>
       <c r="R10" t="n">
-        <v>6593441</v>
+        <v>6593359</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1632,7 +1632,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -2232,32 +2232,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128483246</v>
+        <v>128483569</v>
       </c>
       <c r="B16" t="n">
-        <v>91417</v>
+        <v>91466</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>1204</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2267,10 +2267,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>477422</v>
+        <v>477376</v>
       </c>
       <c r="R16" t="n">
-        <v>6593431</v>
+        <v>6593486</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2312,7 +2312,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2339,32 +2339,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128483569</v>
+        <v>128483246</v>
       </c>
       <c r="B17" t="n">
-        <v>91466</v>
+        <v>91417</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1204</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2374,10 +2374,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>477376</v>
+        <v>477422</v>
       </c>
       <c r="R17" t="n">
-        <v>6593486</v>
+        <v>6593431</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2419,7 +2419,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 57378-2020 artfynd.xlsx
+++ b/artfynd/A 57378-2020 artfynd.xlsx
@@ -1886,7 +1886,7 @@
         <v>128482512</v>
       </c>
       <c r="B13" t="n">
-        <v>91417</v>
+        <v>91423</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
         <v>128482605</v>
       </c>
       <c r="B14" t="n">
-        <v>57845</v>
+        <v>57849</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2114,7 +2114,7 @@
         <v>128483143</v>
       </c>
       <c r="B15" t="n">
-        <v>57845</v>
+        <v>57849</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>128483569</v>
       </c>
       <c r="B16" t="n">
-        <v>91466</v>
+        <v>91472</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2342,7 +2342,7 @@
         <v>128483246</v>
       </c>
       <c r="B17" t="n">
-        <v>91417</v>
+        <v>91423</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 57378-2020 artfynd.xlsx
+++ b/artfynd/A 57378-2020 artfynd.xlsx
@@ -890,7 +890,7 @@
         <v>128296497</v>
       </c>
       <c r="B4" t="n">
-        <v>92744</v>
+        <v>92756</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>128296452</v>
       </c>
       <c r="B5" t="n">
-        <v>92744</v>
+        <v>92756</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
         <v>128296673</v>
       </c>
       <c r="B6" t="n">
-        <v>57845</v>
+        <v>57849</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1225,7 +1225,7 @@
         <v>128373243</v>
       </c>
       <c r="B7" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,10 +1348,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128373432</v>
+        <v>128374330</v>
       </c>
       <c r="B8" t="n">
-        <v>92081</v>
+        <v>91429</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1359,21 +1359,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1339</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1383,10 +1383,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>477404</v>
+        <v>477309</v>
       </c>
       <c r="R8" t="n">
-        <v>6593461</v>
+        <v>6593359</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1455,32 +1455,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128373961</v>
+        <v>128373432</v>
       </c>
       <c r="B9" t="n">
-        <v>91466</v>
+        <v>92093</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1204</v>
+        <v>1339</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1490,10 +1490,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>477355</v>
+        <v>477404</v>
       </c>
       <c r="R9" t="n">
-        <v>6593441</v>
+        <v>6593461</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1525,7 +1525,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1562,32 +1562,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128374330</v>
+        <v>128373961</v>
       </c>
       <c r="B10" t="n">
-        <v>91417</v>
+        <v>91478</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>1204</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1597,10 +1597,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>477309</v>
+        <v>477355</v>
       </c>
       <c r="R10" t="n">
-        <v>6593359</v>
+        <v>6593441</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1632,7 +1632,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1672,7 +1672,7 @@
         <v>128373501</v>
       </c>
       <c r="B11" t="n">
-        <v>91417</v>
+        <v>91429</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
         <v>128374049</v>
       </c>
       <c r="B12" t="n">
-        <v>91417</v>
+        <v>91429</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1886,7 +1886,7 @@
         <v>128482512</v>
       </c>
       <c r="B13" t="n">
-        <v>91423</v>
+        <v>91429</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>128483569</v>
       </c>
       <c r="B16" t="n">
-        <v>91472</v>
+        <v>91478</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2342,7 +2342,7 @@
         <v>128483246</v>
       </c>
       <c r="B17" t="n">
-        <v>91423</v>
+        <v>91429</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 57378-2020 artfynd.xlsx
+++ b/artfynd/A 57378-2020 artfynd.xlsx
@@ -1348,10 +1348,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128374330</v>
+        <v>128373432</v>
       </c>
       <c r="B8" t="n">
-        <v>91429</v>
+        <v>92093</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1359,21 +1359,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>1339</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1383,10 +1383,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>477309</v>
+        <v>477404</v>
       </c>
       <c r="R8" t="n">
-        <v>6593359</v>
+        <v>6593461</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1455,32 +1455,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128373432</v>
+        <v>128373961</v>
       </c>
       <c r="B9" t="n">
-        <v>92093</v>
+        <v>91478</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1339</v>
+        <v>1204</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1490,10 +1490,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>477404</v>
+        <v>477355</v>
       </c>
       <c r="R9" t="n">
-        <v>6593461</v>
+        <v>6593441</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1525,7 +1525,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1562,32 +1562,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128373961</v>
+        <v>128374330</v>
       </c>
       <c r="B10" t="n">
-        <v>91478</v>
+        <v>91429</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1204</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1597,10 +1597,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>477355</v>
+        <v>477309</v>
       </c>
       <c r="R10" t="n">
-        <v>6593441</v>
+        <v>6593359</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1632,7 +1632,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 57378-2020 artfynd.xlsx
+++ b/artfynd/A 57378-2020 artfynd.xlsx
@@ -890,7 +890,7 @@
         <v>128296497</v>
       </c>
       <c r="B4" t="n">
-        <v>92756</v>
+        <v>92758</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>128296452</v>
       </c>
       <c r="B5" t="n">
-        <v>92756</v>
+        <v>92758</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
         <v>128373432</v>
       </c>
       <c r="B8" t="n">
-        <v>92093</v>
+        <v>92095</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>128373961</v>
       </c>
       <c r="B9" t="n">
-        <v>91478</v>
+        <v>91480</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         <v>128374330</v>
       </c>
       <c r="B10" t="n">
-        <v>91429</v>
+        <v>91431</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1672,7 +1672,7 @@
         <v>128373501</v>
       </c>
       <c r="B11" t="n">
-        <v>91429</v>
+        <v>91431</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
         <v>128374049</v>
       </c>
       <c r="B12" t="n">
-        <v>91429</v>
+        <v>91431</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1886,7 +1886,7 @@
         <v>128482512</v>
       </c>
       <c r="B13" t="n">
-        <v>91429</v>
+        <v>91431</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>128483569</v>
       </c>
       <c r="B16" t="n">
-        <v>91478</v>
+        <v>91480</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2342,7 +2342,7 @@
         <v>128483246</v>
       </c>
       <c r="B17" t="n">
-        <v>91429</v>
+        <v>91431</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 57378-2020 artfynd.xlsx
+++ b/artfynd/A 57378-2020 artfynd.xlsx
@@ -890,7 +890,7 @@
         <v>128296497</v>
       </c>
       <c r="B4" t="n">
-        <v>92758</v>
+        <v>92759</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>128296452</v>
       </c>
       <c r="B5" t="n">
-        <v>92758</v>
+        <v>92759</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1348,10 +1348,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128373432</v>
+        <v>128374330</v>
       </c>
       <c r="B8" t="n">
-        <v>92095</v>
+        <v>91432</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1359,21 +1359,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1339</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1383,10 +1383,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>477404</v>
+        <v>477309</v>
       </c>
       <c r="R8" t="n">
-        <v>6593461</v>
+        <v>6593359</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1458,7 +1458,7 @@
         <v>128373961</v>
       </c>
       <c r="B9" t="n">
-        <v>91480</v>
+        <v>91481</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1562,10 +1562,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128374330</v>
+        <v>128373432</v>
       </c>
       <c r="B10" t="n">
-        <v>91431</v>
+        <v>92096</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1573,21 +1573,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>1339</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1597,10 +1597,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>477309</v>
+        <v>477404</v>
       </c>
       <c r="R10" t="n">
-        <v>6593359</v>
+        <v>6593461</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1632,7 +1632,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1672,7 +1672,7 @@
         <v>128373501</v>
       </c>
       <c r="B11" t="n">
-        <v>91431</v>
+        <v>91432</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
         <v>128374049</v>
       </c>
       <c r="B12" t="n">
-        <v>91431</v>
+        <v>91432</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1886,7 +1886,7 @@
         <v>128482512</v>
       </c>
       <c r="B13" t="n">
-        <v>91431</v>
+        <v>91432</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2232,32 +2232,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128483569</v>
+        <v>128483246</v>
       </c>
       <c r="B16" t="n">
-        <v>91480</v>
+        <v>91432</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1204</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2267,10 +2267,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>477376</v>
+        <v>477422</v>
       </c>
       <c r="R16" t="n">
-        <v>6593486</v>
+        <v>6593431</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2312,7 +2312,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2339,32 +2339,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128483246</v>
+        <v>128483569</v>
       </c>
       <c r="B17" t="n">
-        <v>91431</v>
+        <v>91481</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>1204</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2374,10 +2374,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>477422</v>
+        <v>477376</v>
       </c>
       <c r="R17" t="n">
-        <v>6593431</v>
+        <v>6593486</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2419,7 +2419,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 57378-2020 artfynd.xlsx
+++ b/artfynd/A 57378-2020 artfynd.xlsx
@@ -1886,7 +1886,7 @@
         <v>128482512</v>
       </c>
       <c r="B13" t="n">
-        <v>91432</v>
+        <v>91459</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
         <v>128482605</v>
       </c>
       <c r="B14" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2114,7 +2114,7 @@
         <v>128483143</v>
       </c>
       <c r="B15" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2232,32 +2232,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128483246</v>
+        <v>128483569</v>
       </c>
       <c r="B16" t="n">
-        <v>91432</v>
+        <v>91508</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>1204</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2267,10 +2267,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>477422</v>
+        <v>477376</v>
       </c>
       <c r="R16" t="n">
-        <v>6593431</v>
+        <v>6593486</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2312,7 +2312,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2339,32 +2339,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128483569</v>
+        <v>128483246</v>
       </c>
       <c r="B17" t="n">
-        <v>91481</v>
+        <v>91459</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1204</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2374,10 +2374,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>477376</v>
+        <v>477422</v>
       </c>
       <c r="R17" t="n">
-        <v>6593486</v>
+        <v>6593431</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2419,7 +2419,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 57378-2020 artfynd.xlsx
+++ b/artfynd/A 57378-2020 artfynd.xlsx
@@ -890,7 +890,7 @@
         <v>128296497</v>
       </c>
       <c r="B4" t="n">
-        <v>92759</v>
+        <v>92786</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>128296452</v>
       </c>
       <c r="B5" t="n">
-        <v>92759</v>
+        <v>92786</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
         <v>128296673</v>
       </c>
       <c r="B6" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1225,7 +1225,7 @@
         <v>128373243</v>
       </c>
       <c r="B7" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,10 +1348,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128374330</v>
+        <v>128373432</v>
       </c>
       <c r="B8" t="n">
-        <v>91432</v>
+        <v>92123</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1359,21 +1359,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>1339</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1383,10 +1383,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>477309</v>
+        <v>477404</v>
       </c>
       <c r="R8" t="n">
-        <v>6593359</v>
+        <v>6593461</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1458,7 +1458,7 @@
         <v>128373961</v>
       </c>
       <c r="B9" t="n">
-        <v>91481</v>
+        <v>91508</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1562,10 +1562,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128373432</v>
+        <v>128374330</v>
       </c>
       <c r="B10" t="n">
-        <v>92096</v>
+        <v>91459</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1573,21 +1573,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1339</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1597,10 +1597,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>477404</v>
+        <v>477309</v>
       </c>
       <c r="R10" t="n">
-        <v>6593461</v>
+        <v>6593359</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1632,7 +1632,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1669,10 +1669,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128373501</v>
+        <v>128374049</v>
       </c>
       <c r="B11" t="n">
-        <v>91432</v>
+        <v>91459</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1704,10 +1704,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>477404</v>
+        <v>477371</v>
       </c>
       <c r="R11" t="n">
-        <v>6593461</v>
+        <v>6593451</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1749,7 +1749,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1776,10 +1776,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128374049</v>
+        <v>128373501</v>
       </c>
       <c r="B12" t="n">
-        <v>91432</v>
+        <v>91459</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1811,10 +1811,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>477371</v>
+        <v>477404</v>
       </c>
       <c r="R12" t="n">
-        <v>6593451</v>
+        <v>6593461</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1846,7 +1846,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1856,7 +1856,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2232,32 +2232,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128483569</v>
+        <v>128483246</v>
       </c>
       <c r="B16" t="n">
-        <v>91508</v>
+        <v>91459</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1204</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2267,10 +2267,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>477376</v>
+        <v>477422</v>
       </c>
       <c r="R16" t="n">
-        <v>6593486</v>
+        <v>6593431</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2312,7 +2312,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2339,32 +2339,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128483246</v>
+        <v>128483569</v>
       </c>
       <c r="B17" t="n">
-        <v>91459</v>
+        <v>91508</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>1204</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2374,10 +2374,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>477422</v>
+        <v>477376</v>
       </c>
       <c r="R17" t="n">
-        <v>6593431</v>
+        <v>6593486</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2419,7 +2419,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 57378-2020 artfynd.xlsx
+++ b/artfynd/A 57378-2020 artfynd.xlsx
@@ -1348,32 +1348,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128373432</v>
+        <v>128373961</v>
       </c>
       <c r="B8" t="n">
-        <v>92123</v>
+        <v>91508</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1339</v>
+        <v>1204</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1383,10 +1383,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>477404</v>
+        <v>477355</v>
       </c>
       <c r="R8" t="n">
-        <v>6593461</v>
+        <v>6593441</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1455,32 +1455,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128373961</v>
+        <v>128373432</v>
       </c>
       <c r="B9" t="n">
-        <v>91508</v>
+        <v>92123</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1204</v>
+        <v>1339</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1490,10 +1490,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>477355</v>
+        <v>477404</v>
       </c>
       <c r="R9" t="n">
-        <v>6593441</v>
+        <v>6593461</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1525,7 +1525,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1669,7 +1669,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128374049</v>
+        <v>128373501</v>
       </c>
       <c r="B11" t="n">
         <v>91459</v>
@@ -1704,10 +1704,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>477371</v>
+        <v>477404</v>
       </c>
       <c r="R11" t="n">
-        <v>6593451</v>
+        <v>6593461</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1749,7 +1749,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1776,7 +1776,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128373501</v>
+        <v>128374049</v>
       </c>
       <c r="B12" t="n">
         <v>91459</v>
@@ -1811,10 +1811,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>477404</v>
+        <v>477371</v>
       </c>
       <c r="R12" t="n">
-        <v>6593461</v>
+        <v>6593451</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1846,7 +1846,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1856,7 +1856,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1886,7 +1886,7 @@
         <v>128482512</v>
       </c>
       <c r="B13" t="n">
-        <v>91459</v>
+        <v>91464</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>128483246</v>
       </c>
       <c r="B16" t="n">
-        <v>91459</v>
+        <v>91464</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2342,7 +2342,7 @@
         <v>128483569</v>
       </c>
       <c r="B17" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 57378-2020 artfynd.xlsx
+++ b/artfynd/A 57378-2020 artfynd.xlsx
@@ -890,7 +890,7 @@
         <v>128296497</v>
       </c>
       <c r="B4" t="n">
-        <v>92786</v>
+        <v>92796</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>128296452</v>
       </c>
       <c r="B5" t="n">
-        <v>92786</v>
+        <v>92796</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1348,32 +1348,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128373961</v>
+        <v>128374330</v>
       </c>
       <c r="B8" t="n">
-        <v>91508</v>
+        <v>91469</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1204</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1383,10 +1383,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>477355</v>
+        <v>477309</v>
       </c>
       <c r="R8" t="n">
-        <v>6593441</v>
+        <v>6593359</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1458,7 +1458,7 @@
         <v>128373432</v>
       </c>
       <c r="B9" t="n">
-        <v>92123</v>
+        <v>92133</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1562,32 +1562,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128374330</v>
+        <v>128373961</v>
       </c>
       <c r="B10" t="n">
-        <v>91459</v>
+        <v>91518</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>1204</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1597,10 +1597,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>477309</v>
+        <v>477355</v>
       </c>
       <c r="R10" t="n">
-        <v>6593359</v>
+        <v>6593441</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1632,7 +1632,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1672,7 +1672,7 @@
         <v>128373501</v>
       </c>
       <c r="B11" t="n">
-        <v>91459</v>
+        <v>91469</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
         <v>128374049</v>
       </c>
       <c r="B12" t="n">
-        <v>91459</v>
+        <v>91469</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1886,7 +1886,7 @@
         <v>128482512</v>
       </c>
       <c r="B13" t="n">
-        <v>91464</v>
+        <v>91469</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2232,32 +2232,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128483246</v>
+        <v>128483569</v>
       </c>
       <c r="B16" t="n">
-        <v>91464</v>
+        <v>91518</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>1204</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2267,10 +2267,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>477422</v>
+        <v>477376</v>
       </c>
       <c r="R16" t="n">
-        <v>6593431</v>
+        <v>6593486</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2312,7 +2312,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2339,32 +2339,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128483569</v>
+        <v>128483246</v>
       </c>
       <c r="B17" t="n">
-        <v>91513</v>
+        <v>91469</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1204</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2374,10 +2374,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>477376</v>
+        <v>477422</v>
       </c>
       <c r="R17" t="n">
-        <v>6593486</v>
+        <v>6593431</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2419,7 +2419,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 57378-2020 artfynd.xlsx
+++ b/artfynd/A 57378-2020 artfynd.xlsx
@@ -1348,10 +1348,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128374330</v>
+        <v>128373432</v>
       </c>
       <c r="B8" t="n">
-        <v>91469</v>
+        <v>92133</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1359,21 +1359,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>1339</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1383,10 +1383,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>477309</v>
+        <v>477404</v>
       </c>
       <c r="R8" t="n">
-        <v>6593359</v>
+        <v>6593461</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1455,32 +1455,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128373432</v>
+        <v>128373961</v>
       </c>
       <c r="B9" t="n">
-        <v>92133</v>
+        <v>91518</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1339</v>
+        <v>1204</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1490,10 +1490,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>477404</v>
+        <v>477355</v>
       </c>
       <c r="R9" t="n">
-        <v>6593461</v>
+        <v>6593441</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1525,7 +1525,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1562,32 +1562,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128373961</v>
+        <v>128374330</v>
       </c>
       <c r="B10" t="n">
-        <v>91518</v>
+        <v>91469</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1204</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1597,10 +1597,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>477355</v>
+        <v>477309</v>
       </c>
       <c r="R10" t="n">
-        <v>6593441</v>
+        <v>6593359</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1632,7 +1632,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 57378-2020 artfynd.xlsx
+++ b/artfynd/A 57378-2020 artfynd.xlsx
@@ -1886,7 +1886,7 @@
         <v>128482512</v>
       </c>
       <c r="B13" t="n">
-        <v>91469</v>
+        <v>91473</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
         <v>128482605</v>
       </c>
       <c r="B14" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2114,7 +2114,7 @@
         <v>128483143</v>
       </c>
       <c r="B15" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>128483569</v>
       </c>
       <c r="B16" t="n">
-        <v>91518</v>
+        <v>91522</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2342,7 +2342,7 @@
         <v>128483246</v>
       </c>
       <c r="B17" t="n">
-        <v>91469</v>
+        <v>91473</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 57378-2020 artfynd.xlsx
+++ b/artfynd/A 57378-2020 artfynd.xlsx
@@ -1225,7 +1225,7 @@
         <v>128373243</v>
       </c>
       <c r="B7" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,10 +1348,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128373432</v>
+        <v>128374330</v>
       </c>
       <c r="B8" t="n">
-        <v>92133</v>
+        <v>91473</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1359,21 +1359,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1339</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1383,10 +1383,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>477404</v>
+        <v>477309</v>
       </c>
       <c r="R8" t="n">
-        <v>6593461</v>
+        <v>6593359</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1455,32 +1455,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128373961</v>
+        <v>128373432</v>
       </c>
       <c r="B9" t="n">
-        <v>91518</v>
+        <v>92137</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1204</v>
+        <v>1339</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1490,10 +1490,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>477355</v>
+        <v>477404</v>
       </c>
       <c r="R9" t="n">
-        <v>6593441</v>
+        <v>6593461</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1525,7 +1525,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1562,32 +1562,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128374330</v>
+        <v>128373961</v>
       </c>
       <c r="B10" t="n">
-        <v>91469</v>
+        <v>91522</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>1204</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1597,10 +1597,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>477309</v>
+        <v>477355</v>
       </c>
       <c r="R10" t="n">
-        <v>6593359</v>
+        <v>6593441</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1632,7 +1632,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1672,7 +1672,7 @@
         <v>128373501</v>
       </c>
       <c r="B11" t="n">
-        <v>91469</v>
+        <v>91473</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
         <v>128374049</v>
       </c>
       <c r="B12" t="n">
-        <v>91469</v>
+        <v>91473</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2232,32 +2232,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128483569</v>
+        <v>128483246</v>
       </c>
       <c r="B16" t="n">
-        <v>91522</v>
+        <v>91473</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1204</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2267,10 +2267,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>477376</v>
+        <v>477422</v>
       </c>
       <c r="R16" t="n">
-        <v>6593486</v>
+        <v>6593431</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2312,7 +2312,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2339,32 +2339,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128483246</v>
+        <v>128483569</v>
       </c>
       <c r="B17" t="n">
-        <v>91473</v>
+        <v>91522</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>1204</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2374,10 +2374,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>477422</v>
+        <v>477376</v>
       </c>
       <c r="R17" t="n">
-        <v>6593431</v>
+        <v>6593486</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2419,7 +2419,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 57378-2020 artfynd.xlsx
+++ b/artfynd/A 57378-2020 artfynd.xlsx
@@ -1348,10 +1348,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128374330</v>
+        <v>128373432</v>
       </c>
       <c r="B8" t="n">
-        <v>91473</v>
+        <v>92137</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1359,21 +1359,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>1339</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1383,10 +1383,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>477309</v>
+        <v>477404</v>
       </c>
       <c r="R8" t="n">
-        <v>6593359</v>
+        <v>6593461</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1455,32 +1455,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128373432</v>
+        <v>128373961</v>
       </c>
       <c r="B9" t="n">
-        <v>92137</v>
+        <v>91522</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1339</v>
+        <v>1204</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1490,10 +1490,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>477404</v>
+        <v>477355</v>
       </c>
       <c r="R9" t="n">
-        <v>6593461</v>
+        <v>6593441</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1525,7 +1525,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1562,32 +1562,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128373961</v>
+        <v>128374330</v>
       </c>
       <c r="B10" t="n">
-        <v>91522</v>
+        <v>91473</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1204</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1597,10 +1597,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>477355</v>
+        <v>477309</v>
       </c>
       <c r="R10" t="n">
-        <v>6593441</v>
+        <v>6593359</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1632,7 +1632,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -2232,32 +2232,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128483246</v>
+        <v>128483569</v>
       </c>
       <c r="B16" t="n">
-        <v>91473</v>
+        <v>91522</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>1204</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2267,10 +2267,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>477422</v>
+        <v>477376</v>
       </c>
       <c r="R16" t="n">
-        <v>6593431</v>
+        <v>6593486</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2312,7 +2312,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2339,32 +2339,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128483569</v>
+        <v>128483246</v>
       </c>
       <c r="B17" t="n">
-        <v>91522</v>
+        <v>91473</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1204</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2374,10 +2374,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>477376</v>
+        <v>477422</v>
       </c>
       <c r="R17" t="n">
-        <v>6593486</v>
+        <v>6593431</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2419,7 +2419,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 57378-2020 artfynd.xlsx
+++ b/artfynd/A 57378-2020 artfynd.xlsx
@@ -1225,7 +1225,7 @@
         <v>128373243</v>
       </c>
       <c r="B7" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
         <v>128373432</v>
       </c>
       <c r="B8" t="n">
-        <v>92137</v>
+        <v>92142</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>128373961</v>
       </c>
       <c r="B9" t="n">
-        <v>91522</v>
+        <v>91527</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         <v>128374330</v>
       </c>
       <c r="B10" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1672,7 +1672,7 @@
         <v>128373501</v>
       </c>
       <c r="B11" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
         <v>128374049</v>
       </c>
       <c r="B12" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1886,7 +1886,7 @@
         <v>128482512</v>
       </c>
       <c r="B13" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
         <v>128482605</v>
       </c>
       <c r="B14" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2114,7 +2114,7 @@
         <v>128483143</v>
       </c>
       <c r="B15" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>128483569</v>
       </c>
       <c r="B16" t="n">
-        <v>91522</v>
+        <v>91527</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2342,7 +2342,7 @@
         <v>128483246</v>
       </c>
       <c r="B17" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
